--- a/data/result_20260904_101858 (user extra extra info).xlsx
+++ b/data/result_20260904_101858 (user extra extra info).xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{97C7416B-E0FB-427C-8232-40B260F128B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4669EA31-E876-4E6E-AD0E-BDE9FD715C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results export" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results export'!$A$1:$U$17</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="95">
   <si>
     <t>user_id</t>
   </si>
@@ -318,13 +319,16 @@
   </si>
   <si>
     <t>Vietnam</t>
+  </si>
+  <si>
+    <t>device_share</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -332,13 +336,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -353,8 +369,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1823,4 +1841,220 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <picture r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FC3CC9-5560-4E7D-88F0-229BE502E7A0}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="34.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <f>COUNTIFS($B$2:$B$17,B2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C17" si="0">COUNTIFS($B$2:$B$17,B3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>